--- a/Regelsæt.xlsx
+++ b/Regelsæt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\RPA\Leverancer\Påmindelse om afregning af indsatser voksne\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2F9C6A-3E84-49E5-8B39-27E54C9B6F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2367DE-AC12-4D7B-BC49-F3EE1B5DAE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Regler" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Organisationer</t>
   </si>
@@ -51,15 +51,6 @@
     <t>Fremtidigt ændret</t>
   </si>
   <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Voksenrådgivningen</t>
   </si>
   <si>
@@ -120,46 +111,22 @@
     <t>Bjerggårdshaven Hus 3</t>
   </si>
   <si>
-    <t>Ungerådgivningen - Særlig funktion</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 1 - Vagt &amp; Visitation</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Kompensation</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Bevilliget</t>
   </si>
   <si>
-    <t>Kontaktperson og Bostøtte Unge 1</t>
-  </si>
-  <si>
-    <t>Kontaktperson og Bostøtte Unge 2</t>
-  </si>
-  <si>
-    <t>Kontaktperson og Bostøtte Unge 3</t>
-  </si>
-  <si>
-    <t>Kontaktperson og Bostøtte Unge 4</t>
-  </si>
-  <si>
-    <t>Bostøtte - Over 30 år</t>
+    <t>Social og jobrådgivningen</t>
+  </si>
+  <si>
+    <t>Specialenheden</t>
+  </si>
+  <si>
+    <t>Social og udvikling</t>
+  </si>
+  <si>
+    <t>Bostøtte Voksne</t>
+  </si>
+  <si>
+    <t>Social og jobindsatser</t>
   </si>
 </sst>
 </file>
@@ -489,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="47.140625" bestFit="1" customWidth="1"/>
@@ -510,21 +477,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>3</v>
@@ -532,10 +499,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -543,141 +510,104 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
